--- a/sheets/대금율보/검수/잘있거라 황진이.xlsx
+++ b/sheets/대금율보/검수/잘있거라 황진이.xlsx
@@ -4097,8 +4097,7 @@
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-潕
-‹</t>
+潕</t>
         </is>
       </c>
       <c r="E4" s="23" t="inlineStr">
@@ -4291,11 +4290,7 @@
         </is>
       </c>
       <c r="I9" s="23"/>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J9" s="21"/>
       <c r="K9" s="23"/>
     </row>
     <row r="10" ht="56" customHeight="1">
@@ -4504,8 +4499,7 @@
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林∧
-‹</t>
+          <t xml:space="preserve">林∧</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -4559,11 +4553,7 @@
           <t xml:space="preserve">는간</t>
         </is>
       </c>
-      <c r="J16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J16" s="21"/>
       <c r="K16" s="23"/>
     </row>
     <row r="17" ht="56" customHeight="1">
@@ -4572,8 +4562,7 @@
       <c r="C17" s="23"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -4623,16 +4612,11 @@
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="G18" s="26"/>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H18" s="21"/>
       <c r="I18" s="26"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
@@ -4745,8 +4729,7 @@
       <c r="F21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰
-–汰
-‹</t>
+–汰</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -4845,8 +4828,7 @@
       </c>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -4866,11 +4848,7 @@
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D24" s="21"/>
       <c r="E24" s="23"/>
       <c r="F24" s="21" t="inlineStr">
         <is>

--- a/sheets/대금율보/검수/잘있거라 황진이.xlsx
+++ b/sheets/대금율보/검수/잘있거라 황진이.xlsx
@@ -4009,22 +4009,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="69.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="69.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
       <c r="J4" s="21"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="69.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="69.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="24" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="K6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="69.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="69.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -4267,7 +4267,7 @@
       <c r="J8" s="21"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="69.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -4293,7 +4293,7 @@
       <c r="J9" s="21"/>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="69.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="26"/>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="K10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="69.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="69.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -4402,7 +4402,7 @@
       <c r="J12" s="21"/>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="69.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="69.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="K14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="69.36" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="69.36" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -4556,7 +4556,7 @@
       <c r="J16" s="21"/>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="69.36" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="69.36" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="K18" s="26"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="69.36" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="K19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="69.36" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="23"/>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="K20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="69.36" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="K21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="69.36" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="26"/>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="K22" s="26"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="69.36" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="K23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="69.36" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="K24" s="23"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="69.36" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="23"/>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="K25" s="23"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="69.36" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="26"/>
@@ -4950,6 +4950,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
 </worksheet>
 </file>